--- a/docentes/Cruz Alejo José Armando - Estadisticos 20211.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -76,13 +76,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>JOSE JAZAEL</t>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>TEPOLE</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>MUÑOZ</t>
+  </si>
+  <si>
+    <t>YAHIR</t>
+  </si>
+  <si>
+    <t>JOHNNY</t>
   </si>
 </sst>
 </file>
@@ -483,19 +492,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>81.25</v>
+        <v>87.5</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -509,19 +518,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>68.42</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -535,19 +544,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>68.75</v>
+        <v>78.13</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -600,16 +609,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>84.38</v>
+      </c>
+      <c r="H2">
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -623,16 +635,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>81.58</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -646,16 +661,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>78.13</v>
+      </c>
+      <c r="H4">
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -708,19 +726,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>81.25</v>
+        <v>84.38</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -734,19 +752,19 @@
         <v>38</v>
       </c>
       <c r="D3">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>68.42</v>
+        <v>81.58</v>
       </c>
       <c r="H3">
-        <v>8.699999999999999</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -760,19 +778,19 @@
         <v>32</v>
       </c>
       <c r="D4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G4">
-        <v>68.75</v>
+        <v>78.13</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.1</v>
       </c>
     </row>
   </sheetData>
@@ -782,7 +800,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -814,25 +832,48 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920085</v>
+        <v>20330051920050</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920034</v>
+      </c>
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>7</v>
+      <c r="F3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20211.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20211.xlsx
@@ -873,7 +873,7 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Cruz Alejo José Armando - Estadisticos 20211.xlsx
+++ b/docentes/Cruz Alejo José Armando - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -76,22 +76,13 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>TEPOLE</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>MUÑOZ</t>
-  </si>
-  <si>
-    <t>YAHIR</t>
-  </si>
-  <si>
-    <t>JOHNNY</t>
+    <t>VEGA</t>
+  </si>
+  <si>
+    <t>MENCIAS</t>
+  </si>
+  <si>
+    <t>ALAN EDUARDO</t>
   </si>
 </sst>
 </file>
@@ -729,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>84.38</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -755,13 +746,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G3">
-        <v>81.58</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="H3">
         <v>7.7</v>
@@ -781,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>78.13</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
     </row>
   </sheetData>
@@ -800,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -832,47 +823,24 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920050</v>
+        <v>19330051920039</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
       <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920034</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3">
         <v>2</v>
       </c>
     </row>
